--- a/DOSSIES_MULTIFORMATO/SNPH/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SNPH/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00446</t>
+          <t>2020NE00449</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1929.07</v>
+        <v>1805.81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE00449</t>
+          <t>2020NE00446</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1805.81</v>
+        <v>1929.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -744,12 +744,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020NE00219</t>
+          <t>2020NE00218</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12704.68</v>
+        <v>2571.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -767,19 +767,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO (PORTAL DE TRANSPARÊNCIA), NO PERÍODO DE 12 (DOZE) MESES.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020NE00218</t>
+          <t>2020NE00219</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2571.4</v>
+        <v>12704.68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO (PORTAL DE TRANSPARÊNCIA), NO PERÍODO DE 12 (DOZE) MESES.</t>
+          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024NE0000346</t>
+          <t>2024NE0000345</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4634.31</v>
+        <v>521.23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -853,19 +853,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024NE0000345</t>
+          <t>2024NE0000346</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>521.23</v>
+        <v>4634.31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000192</t>
+          <t>2025NE0000191</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1042.46</v>
+        <v>5678.26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
+          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025NE0000191</t>
+          <t>2025NE0000192</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5678.26</v>
+        <v>1042.46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1003,19 +1003,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025NE0000126</t>
+          <t>2025NE0000127</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5678.26</v>
+        <v>1042.46</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025NE0000127</t>
+          <t>2025NE0000126</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1042.46</v>
+        <v>5678.26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
+          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022NE0000132</t>
+          <t>2022NE0000130</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2050.88</v>
+        <v>1598.44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE ACESSO À INTRNET E SERVIÇO DE TRANSMISSÃO DE DADOS DA SNPH.</t>
+          <t>REFERENTE PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSPARÊNCIA DA SNPH.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2022NE0000130</t>
+          <t>2022NE0000132</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1598.44</v>
+        <v>2050.88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>REFERENTE PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSPARÊNCIA DA SNPH.</t>
+          <t>REFERENTE SERVIÇO DE ACESSO À INTRNET E SERVIÇO DE TRANSMISSÃO DE DADOS DA SNPH.</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2022NE0000229</t>
+          <t>2022NE0000228</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2472.72</v>
+        <v>486.48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1309,19 +1309,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2022NE0000228</t>
+          <t>2022NE0000229</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>486.48</v>
+        <v>2472.72</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1339,19 +1339,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
+          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00264</t>
+          <t>2016NE00263</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>976.04</v>
+        <v>3381.32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1369,19 +1369,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO PARA SNPH.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016NE00263</t>
+          <t>2016NE00264</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3381.32</v>
+        <v>976.04</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1399,19 +1399,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO PARA SNPH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2023NE0000251</t>
+          <t>2023NE0000250</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2643.26</v>
+        <v>555.98</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 029/2022-PROJU/SNPH, em 11/07/2022. TC: 004/2019 AD: 03.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 027/2022-PROJU/SNPH, em 05/07/2022. TC: 005/2020 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2023NE0000250</t>
+          <t>2023NE0000251</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>555.98</v>
+        <v>2643.26</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1459,28 +1459,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 027/2022-PROJU/SNPH, em 05/07/2022. TC: 005/2020 AD: 02.</t>
+          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 029/2022-PROJU/SNPH, em 11/07/2022. TC: 004/2019 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2019NE00298</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5/2014</t>
-        </is>
-      </c>
+          <t>2019NE00301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>28/06/2019</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1747.47</v>
+        <v>554.9299999999999</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1489,7 +1485,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS.</t>
+          <t>Contratação de empresa especializada em desenvolvimento de Website Institucional - Portal de transparencia da SNPH.</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1522,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2019NE00301</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>2019NE00298</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5/2014</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>28/06/2019</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>554.9299999999999</v>
+        <v>1747.47</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em desenvolvimento de Website Institucional - Portal de transparencia da SNPH.</t>
+          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2023NE0000185</t>
+          <t>2023NE0000190</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1042.46</v>
+        <v>2050.88</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1575,19 +1575,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
+          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2023NE0000190</t>
+          <t>2023NE0000185</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2050.88</v>
+        <v>1042.46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1605,19 +1605,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018NE00075</t>
+          <t>2018NE00074</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3156.18</v>
+        <v>10484.82</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1635,19 +1635,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA, REAJUSTE DE 3,36% RE</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018NE00074</t>
+          <t>2018NE00075</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10484.82</v>
+        <v>3156.18</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1665,19 +1665,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA, REAJUSTE DE 3,36% RE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2023NE0000357</t>
+          <t>2023NE0000356</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2557.99</v>
+        <v>4634.31</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2023NE0000356</t>
+          <t>2023NE0000357</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4634.31</v>
+        <v>2557.99</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1755,14 +1755,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2019NE00374</t>
+          <t>2019NE00378</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP)</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP).</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2019NE00378</t>
+          <t>2019NE00374</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1841,19 +1841,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023NE0000285</t>
+          <t>2023NE00284</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>486.48</v>
+        <v>2472.72</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1871,19 +1871,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de hospedagem de Sistema de Informação - Portal de Transparência da SNPH.</t>
+          <t>4º Termo Aditivo ao Contrato 004/2019 - Prorrogação de prazo</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2023NE0000284</t>
+          <t>2023NE00285</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2472.72</v>
+        <v>486.48</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1901,19 +1901,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Contratação de empresa para execução do sistema PRODAMRH Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
+          <t>3ºT Termo Aditivo, prorrogação de prazo</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2023NE00285</t>
+          <t>2023NE0000284</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>486.48</v>
+        <v>2472.72</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3ºT Termo Aditivo, prorrogação de prazo</t>
+          <t>Contratação de empresa para execução do sistema PRODAMRH Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023NE00284</t>
+          <t>2023NE0000285</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2472.72</v>
+        <v>486.48</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1961,28 +1961,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4º Termo Aditivo ao Contrato 004/2019 - Prorrogação de prazo</t>
+          <t>Contratação de empresa para prestação de serviço de hospedagem de Sistema de Informação - Portal de Transparência da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6/2015</t>
-        </is>
-      </c>
+          <t>2018NE00062</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>27/02/2018</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>520.25</v>
+        <v>3676.43</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1991,7 +1987,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cota para empenhamento de serviço de hospedagem de web site, no periodo de setembro/17.</t>
+          <t>Anulação total conforme Orientação Técnica nº 12/2018-GINS que trata das naturezas de despesas 339040.XX.</t>
         </is>
       </c>
     </row>
@@ -2024,17 +2020,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018NE00062</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>2018NE00067</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>6/2015</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>27/02/2018</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3676.43</v>
+        <v>520.25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anulação total conforme Orientação Técnica nº 12/2018-GINS que trata das naturezas de despesas 339040.XX.</t>
+          <t>Cota para empenhamento de serviço de hospedagem de web site, no periodo de setembro/17.</t>
         </is>
       </c>
     </row>
@@ -2106,14 +2106,10 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018NE00224</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>6/2015</t>
-        </is>
-      </c>
+          <t>2018NE00223</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>26/07/2018</t>
@@ -2129,17 +2125,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
+          <t>anulação total devido a erro na modalidade de pagamento</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018NE00223</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>2018NE00224</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6/2015</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>26/07/2018</t>
@@ -2155,19 +2155,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>anulação total devido a erro na modalidade de pagamento</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025NE0000062</t>
+          <t>2025NE0000063</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9268.620000000001</v>
+        <v>1042.46</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025NE0000063</t>
+          <t>2025NE0000062</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1042.46</v>
+        <v>9268.620000000001</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2018NE00218</t>
+          <t>2018NE00217</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2566.57</v>
+        <v>8737.35</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2305,19 +2305,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018NE00217</t>
+          <t>2018NE00218</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8737.35</v>
+        <v>2566.57</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2022NE0000352</t>
+          <t>2022NE0000353</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>521.23</v>
+        <v>4394.76</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
+          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2022NE0000353</t>
+          <t>2022NE0000352</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4394.76</v>
+        <v>521.23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2015NE00599</t>
+          <t>2015NE00600</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4546.44</v>
+        <v>1363.38</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2015NE00600</t>
+          <t>2015NE00599</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1363.38</v>
+        <v>4546.44</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2570,12 +2570,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020NE00274</t>
+          <t>2020NE00278</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2296.04</v>
+        <v>33137.7</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2593,19 +2593,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SERVIÇO DE WEBSITE PARA SNPH. 4º TERMO ADITIVO DO CONTRATO 06/2015. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ</t>
+          <t>REFERENTE A SERVIÇO DE INTERNET PARA SNPH. CONTRATO 02/2020. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020NE00280</t>
+          <t>2020NE00279</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2571.4</v>
+        <v>12704.68</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>REFERENTE AO SISTEMA DE WEBSITE PARA A SNPH. CONTRATO 005/2020. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ.</t>
+          <t>REFERENTE AO SISTEMA CFPP DA FOLHA DE PAGAMENTO DA SNPH. 1º TERMO ADITIVO DO CONTRATO Nº 004/2019.</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2660,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020NE00279</t>
+          <t>2020NE00280</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12704.68</v>
+        <v>2571.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2683,19 +2683,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>REFERENTE AO SISTEMA CFPP DA FOLHA DE PAGAMENTO DA SNPH. 1º TERMO ADITIVO DO CONTRATO Nº 004/2019.</t>
+          <t>REFERENTE AO SISTEMA DE WEBSITE PARA A SNPH. CONTRATO 005/2020. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020NE00278</t>
+          <t>2020NE00274</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>33137.7</v>
+        <v>2296.04</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>REFERENTE A SERVIÇO DE INTERNET PARA SNPH. CONTRATO 02/2020. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ.</t>
+          <t>SERVIÇO DE WEBSITE PARA SNPH. 4º TERMO ADITIVO DO CONTRATO 06/2015. REFEITO O EMPENHO DEVIDO A FRUSTRAÇÃO NA RECEITA DA FONTE 145, EMPENHADO NA FONTE 121, CONFORME ORIENTAÇÃO DA SEFAZ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2016NE00368</t>
+          <t>2016NE00369</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>504.86</v>
+        <v>1690.66</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2743,19 +2743,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SERVIÇO DE WEBSITE PARA A SNPH DO MES DE NOV/2016.</t>
+          <t>REFERENTE A SERVIÇO DE PROCESSAMENTOS DAS FOLHAS DE PAGAMENTO DO MES DE NOV/16.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2016NE00369</t>
+          <t>2016NE00368</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1690.66</v>
+        <v>504.86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2773,19 +2773,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>REFERENTE A SERVIÇO DE PROCESSAMENTOS DAS FOLHAS DE PAGAMENTO DO MES DE NOV/16.</t>
+          <t>SERVIÇO DE WEBSITE PARA A SNPH DO MES DE NOV/2016.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2023NE0000415</t>
+          <t>2023NE0000413</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4634.31</v>
+        <v>521.23</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2840,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023NE0000413</t>
+          <t>2023NE0000415</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>521.23</v>
+        <v>4634.31</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2863,19 +2863,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2015NE00350</t>
+          <t>2015NE00351</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>9492.190000000001</v>
+        <v>7577.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Desenvolvimento de WEBSITE</t>
+          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2930,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2015NE00351</t>
+          <t>2015NE00350</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7577.4</v>
+        <v>9492.190000000001</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
+          <t>Desenvolvimento de WEBSITE</t>
         </is>
       </c>
     </row>
@@ -2990,21 +2990,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024NE0000292</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>5/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000291</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>19/09/2024</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>521.23</v>
+        <v>522</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3013,24 +3009,28 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
+          <t>Anulação devido encerramento de contrato.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024NE0000291</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>2024NE0000292</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5/2020</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>19/09/2024</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>522</v>
+        <v>521.23</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anulação devido encerramento de contrato.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020NE00269</t>
+          <t>2020NE00268</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2571.4</v>
+        <v>33137.7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020NE00270</t>
+          <t>2020NE00255</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12704.68</v>
+        <v>2296.04</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020NE00255</t>
+          <t>2020NE00270</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2296.04</v>
+        <v>12704.68</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020NE00268</t>
+          <t>2020NE00269</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>33137.7</v>
+        <v>2571.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3236,12 +3236,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2021NE0000219</t>
+          <t>2021NE0000218</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17579.04</v>
+        <v>10231.96</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>REFERENTE AO CONTRATO DE SERVIÇO DE INTERNET PARA A SNPH</t>
+          <t>REFERENTE AO CONTRATO DO SISTEMA DE FOLHA DE PAGAMENTO DA SNPH</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2021NE0000218</t>
+          <t>2021NE0000219</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10231.96</v>
+        <v>17579.04</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>REFERENTE AO CONTRATO DO SISTEMA DE FOLHA DE PAGAMENTO DA SNPH</t>
+          <t>REFERENTE AO CONTRATO DE SERVIÇO DE INTERNET PARA A SNPH</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3592,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024NE0000058</t>
+          <t>2024NE0000059</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9268.620000000001</v>
+        <v>1042.46</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3652,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024NE0000059</t>
+          <t>2024NE0000058</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1042.46</v>
+        <v>9268.620000000001</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2023NE0000322</t>
+          <t>2023NE0000324</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>521.23</v>
+        <v>2557.99</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2023NE0000324</t>
+          <t>2023NE0000322</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2557.99</v>
+        <v>521.23</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3821,19 +3821,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2017NE00104</t>
+          <t>2017NE00108</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1548.26</v>
+        <v>5071.98</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3851,19 +3851,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1º TACT AO CONTRATO 006/2015 REFERENTE SERVIÇO DE HOSPEDAGEM DE WEBSITE DO PORTAL DE TRANSPARÊNCIA DA SNPH.</t>
+          <t>2º TACT Nº 005/2014 REFERENTE SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO E FOLHA DE PESSOAL PARA A SNPH.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2017NE00108</t>
+          <t>2017NE00104</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5071.98</v>
+        <v>1548.26</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3881,19 +3881,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2º TACT Nº 005/2014 REFERENTE SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO E FOLHA DE PESSOAL PARA A SNPH.</t>
+          <t>1º TACT AO CONTRATO 006/2015 REFERENTE SERVIÇO DE HOSPEDAGEM DE WEBSITE DO PORTAL DE TRANSPARÊNCIA DA SNPH.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2016NE00327</t>
+          <t>2016NE00326</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1690.66</v>
+        <v>504.86</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3911,19 +3911,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SERVIÇO DE FOLHA DE PAGAMENTO DO SISTEMA CFPP DA PRODAM</t>
+          <t>REFERENTE SERVIÇO DE WEBSITE PARA A SNPH</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2016NE00327</t>
+          <t>2016NE00326</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1690.66</v>
+        <v>504.86</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3941,19 +3941,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SERVIÇO DE FOLHA DE PAGAMENTO DO SISTEMA CFPP DA PRODAM</t>
+          <t>REFERENTE SERVIÇO DE WEBSITE PARA A SNPH</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2016NE00326</t>
+          <t>2016NE00327</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>504.86</v>
+        <v>1690.66</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3971,19 +3971,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE WEBSITE PARA A SNPH</t>
+          <t>SERVIÇO DE FOLHA DE PAGAMENTO DO SISTEMA CFPP DA PRODAM</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2016NE00326</t>
+          <t>2016NE00327</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>504.86</v>
+        <v>1690.66</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE WEBSITE PARA A SNPH</t>
+          <t>SERVIÇO DE FOLHA DE PAGAMENTO DO SISTEMA CFPP DA PRODAM</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024NE0000192</t>
+          <t>2024NE0000191</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2643.26</v>
+        <v>555.98</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2024NE0000191</t>
+          <t>2024NE0000192</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>555.98</v>
+        <v>2643.26</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2016NE00099</t>
+          <t>2016NE00098</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1515.48</v>
+        <v>454.46</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4177,14 +4177,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE NOVEMBRO/2015.</t>
+          <t>REFERENTE SERVIÇO DE HOSPEDAGEM DO PORTAL DE TRANSPARENCIA DA SNPH NO PERIODO DE DEZEMBRO/2015.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2016NE00101</t>
+          <t>2016NE00100</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE OUTUBRO/2015.</t>
+          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE DEZEMBRO/2015.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2016NE00100</t>
+          <t>2016NE00101</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4237,19 +4237,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE DEZEMBRO/2015.</t>
+          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE OUTUBRO/2015.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2016NE00098</t>
+          <t>2016NE00099</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>454.46</v>
+        <v>1515.48</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4267,19 +4267,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇO DE HOSPEDAGEM DO PORTAL DE TRANSPARENCIA DA SNPH NO PERIODO DE DEZEMBRO/2015.</t>
+          <t>REFERENTE SERVIÇO DE CAD/FOLHA DE PAGAMENTO DOS SERVIDORES DA SNPH NO PERIODO DE NOVEMBRO/2015.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2021NE0000101</t>
+          <t>2021NE0000103</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7759.24</v>
+        <v>1598.44</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO (PORTAL DE TRANSPARÊNCIA), NO PERÍODO DE 12 (DOZE) MESES.</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2021NE0000103</t>
+          <t>2021NE0000101</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1598.44</v>
+        <v>7759.24</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4357,19 +4357,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO (PORTAL DE TRANSPARÊNCIA), NO PERÍODO DE 12 (DOZE) MESES.</t>
+          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025NE0000274</t>
+          <t>2025NE0000273</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2/2025</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4633.7</v>
+        <v>2839.13</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4387,19 +4387,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Prestação de serviço, de forma dedicada, de acesso à internet por fibra óptica com garantia de 100% em download e upload e serviço de transmissão de circuito de transmissão de dados para conexão clien</t>
+          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025NE0000273</t>
+          <t>2025NE0000274</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2839.13</v>
+        <v>4633.7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
+          <t>Prestação de serviço, de forma dedicada, de acesso à internet por fibra óptica com garantia de 100% em download e upload e serviço de transmissão de circuito de transmissão de dados para conexão clien</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2022NE0000257</t>
+          <t>2022NE0000258</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5115.98</v>
+        <v>1042.46</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2022NE0000258</t>
+          <t>2022NE0000257</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1042.46</v>
+        <v>5115.98</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4507,19 +4507,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
+          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2018NE00230</t>
+          <t>2018NE00229</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1747.47</v>
+        <v>520.25</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4537,19 +4537,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>REFERENTE A PAGAMENTO POR INDENIZAÇÃO DA PRODAM NOTA FISCAL Nº 3141, FOLHA DE PAGAMENTO.</t>
+          <t>RECONHECIMENTO INDENIZATÓRIO DA PRODAM NOTA FISCAL Nº 2900</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2018NE00229</t>
+          <t>2018NE00230</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>520.25</v>
+        <v>1747.47</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4567,24 +4567,28 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO INDENIZATÓRIO DA PRODAM NOTA FISCAL Nº 2900</t>
+          <t>REFERENTE A PAGAMENTO POR INDENIZAÇÃO DA PRODAM NOTA FISCAL Nº 3141, FOLHA DE PAGAMENTO.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024NE0000352</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2024NE0000354</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>07/11/2024</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2839.13</v>
+        <v>4634.31</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4593,7 +4597,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -4630,21 +4634,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2024NE0000354</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000352</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>07/11/2024</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4634.31</v>
+        <v>2839.13</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2017NE00207</t>
+          <t>2017NE00206</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1747.47</v>
+        <v>485.57</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4735,19 +4735,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2017NE00206</t>
+          <t>2017NE00207</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>485.57</v>
+        <v>1747.47</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2020NE00361</t>
+          <t>2020NE00362</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>564.6</v>
+        <v>37.64</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em jul/20, conforme a nf nº 15698.</t>
+          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em ago/20 (02 dias em agosto), conforme a nf nº 16010.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2020NE00360</t>
+          <t>2020NE00358</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em jun/20, conforme a nf nº 15182.</t>
+          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em abril/20, conforme a nf nº 14280.</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020NE00358</t>
+          <t>2020NE00360</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4885,14 +4885,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em abril/20, conforme a nf nº 14280.</t>
+          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em jun/20, conforme a nf nº 15182.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020NE00362</t>
+          <t>2020NE00361</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>37.64</v>
+        <v>564.6</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em ago/20 (02 dias em agosto), conforme a nf nº 16010.</t>
+          <t>Referente pagamento indenizatorio devido a frustração de receita na fonte 145, do serviço de hospedagem de site da SNPH em jul/20, conforme a nf nº 15698.</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025NE0000129</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>2025NE0000130</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
           <t>05/05/2025</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9268.620000000001</v>
+        <v>2162.68</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4967,28 +4971,24 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Anulação devido valores incorretos.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025NE0000130</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2025NE0000129</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>05/05/2025</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2162.68</v>
+        <v>9268.620000000001</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Anulação devido valores incorretos.</t>
         </is>
       </c>
     </row>
@@ -5034,21 +5034,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026NE0000017</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2/2025</t>
-        </is>
-      </c>
+          <t>2026NE0000006</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>18534.8</v>
+        <v>6367.24</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5057,7 +5053,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Prestação de serviço, de forma dedicada, de acesso à internet por fibra óptica com garantia de 100% em download e upload e serviço de transmissão de circuito de transmissão de dados para conexão clien</t>
+          <t>Contratação de serviço de hospedagem do Portal da Transparência da SNPH, - licença de uso do sistema gestor de conteúdo web - GERWEB.</t>
         </is>
       </c>
     </row>
@@ -5090,17 +5086,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026NE0000006</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>2026NE0000017</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2/2025</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>6367.24</v>
+        <v>18534.8</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Contratação de serviço de hospedagem do Portal da Transparência da SNPH, - licença de uso do sistema gestor de conteúdo web - GERWEB.</t>
+          <t>Prestação de serviço, de forma dedicada, de acesso à internet por fibra óptica com garantia de 100% em download e upload e serviço de transmissão de circuito de transmissão de dados para conexão clien</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5146,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2022NE0000308</t>
+          <t>2022NE0000309</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2557.99</v>
+        <v>521.23</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
+          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5206,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2022NE0000309</t>
+          <t>2022NE0000308</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>521.23</v>
+        <v>2557.99</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Segunda prorrogação de prazo do contrato de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH.</t>
+          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021NE0000025</t>
+          <t>2021NE0000026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10231.96</v>
+        <v>17595.24</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
+          <t>Prestação de serviços de acesso a internet com link dedicado de 10 (dez) Mbps, pelo periodo de 12 meses.</t>
         </is>
       </c>
     </row>
@@ -5356,12 +5356,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021NE0000026</t>
+          <t>2021NE0000025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>17595.24</v>
+        <v>10231.96</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5379,14 +5379,14 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso a internet com link dedicado de 10 (dez) Mbps, pelo periodo de 12 meses.</t>
+          <t>REFERENTE AO 1º ADITIVO DO CONTRATO COM A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA ( CADASTRO DE PAGAMENTO DE PESSOAL - CFPP ) PARA ATENDER A NECESSIDADE DA SNPH, PERÍODO DE 12 (DO</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2016NE00012</t>
+          <t>2016NE00035</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5409,24 +5409,28 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS.</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE WEBSITE PARA A SNPH</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2016NE00034</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>2016NE00033</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5/2014</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2726.76</v>
+        <v>9092.879999999999</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5435,28 +5439,24 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DEVIDO A ERRO NA FONTE</t>
+          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP PARA FOLHA DE PAGAMENTO DESTA AUTARQUIA</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2016NE00033</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>5/2014</t>
-        </is>
-      </c>
+          <t>2016NE00034</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>9092.879999999999</v>
+        <v>2726.76</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP PARA FOLHA DE PAGAMENTO DESTA AUTARQUIA</t>
+          <t>ANULAÇÃO TOTAL DEVIDO A ERRO NA FONTE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2016NE00035</t>
+          <t>2016NE00012</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE WEBSITE PARA A SNPH</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS.</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2015NE00378</t>
+          <t>2015NE00386</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DESENVOLVEDOR DE WEBSITE</t>
+          <t>SERVIÇO DE WEBSITE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2015NE00385</t>
+          <t>2015NE00380</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DEVIDO A ERRO NA MODALIDADE.</t>
+          <t>ANULAÇÃO TOTAL DEVIDO A AJUSTE DA DESCRIÇÃO DO EMPENHO</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2015NE00380</t>
+          <t>2015NE00385</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DEVIDO A AJUSTE DA DESCRIÇÃO DO EMPENHO</t>
+          <t>ANULAÇÃO TOTAL DEVIDO A ERRO NA MODALIDADE.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2015NE00386</t>
+          <t>2015NE00378</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SERVIÇO DE WEBSITE</t>
+          <t>DESENVOLVEDOR DE WEBSITE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2016NE00207</t>
+          <t>2016NE00206</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1515.48</v>
+        <v>454.46</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5701,19 +5701,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>REFERENTE A SERVIÇO DO SISTEMA CFPP DE FOLHA DE PAGAMENTO</t>
+          <t>REFERENTE A DESENVOLVIMENTO DO WEBSITE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2016NE00206</t>
+          <t>2016NE00207</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>454.46</v>
+        <v>1515.48</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5731,17 +5731,21 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>REFERENTE A DESENVOLVIMENTO DO WEBSITE</t>
+          <t>REFERENTE A SERVIÇO DO SISTEMA CFPP DE FOLHA DE PAGAMENTO</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2024NE0000124</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+          <t>2024NE0000126</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5/2020</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
           <t>03/05/2024</t>
@@ -5757,21 +5761,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Anulação devido dados incorretos.</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2024NE0000126</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>5/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000124</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>03/05/2024</t>
@@ -5787,17 +5787,21 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>Anulação devido dados incorretos.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2022NE0000060</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
+          <t>2022NE0000061</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>4/2019</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr">
         <is>
           <t>03/01/2022</t>
@@ -5813,7 +5817,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DEVIDO DATA INCORRETA.</t>
+          <t>REFERENTE AO 2º TERMO ADITIVO DO CONTRATO Nº 004/2019, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA (CFPP) PARA ATENDER A NECESSIDADE DA SNPH.</t>
         </is>
       </c>
     </row>
@@ -5850,14 +5854,10 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2022NE0000061</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>4/2019</t>
-        </is>
-      </c>
+          <t>2022NE0000060</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>03/01/2022</t>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>REFERENTE AO 2º TERMO ADITIVO DO CONTRATO Nº 004/2019, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA (CFPP) PARA ATENDER A NECESSIDADE DA SNPH.</t>
+          <t>ANULAÇÃO DEVIDO DATA INCORRETA.</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5906,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021NE0000210</t>
+          <t>2021NE0000212</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2472.72</v>
+        <v>486.48</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5929,19 +5929,19 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>REFERENTE AO 2º TERMO ADITIVO DO CONTRATO Nº 004/2019, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA (CFPP) PARA ATENDER A NECESSIDADE DA SNPH.</t>
+          <t>REFERENTE AO 1º ADITIVO DO CONTRATO Nº 005/2021, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMÁTICA (PORTAL DE TRANSPARÊNCIA), PERÍODO DE 12 MESES.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021NE0000212</t>
+          <t>2021NE0000210</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>486.48</v>
+        <v>2472.72</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>REFERENTE AO 1º ADITIVO DO CONTRATO Nº 005/2021, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SISTEMA DE INFORMÁTICA (PORTAL DE TRANSPARÊNCIA), PERÍODO DE 12 MESES.</t>
+          <t>REFERENTE AO 2º TERMO ADITIVO DO CONTRATO Nº 004/2019, EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA (CFPP) PARA ATENDER A NECESSIDADE DA SNPH.</t>
         </is>
       </c>
     </row>
@@ -5996,12 +5996,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2024NE0000120</t>
+          <t>2024NE0000122</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2020</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2317.15</v>
+        <v>1042.46</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -6056,12 +6056,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2024NE0000122</t>
+          <t>2024NE0000120</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1042.46</v>
+        <v>2317.15</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de informática - WEBSITE - Portal da Transparência da SNPH. Parecer nº 038/2023-PROJU/SNPH. TC: 0005/2020 AD: 03.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000003</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>9268.620000000001</v>
+        <v>5678.26</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6176,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025NE0000003</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5678.26</v>
+        <v>9268.620000000001</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6199,19 +6199,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Serviço de execução do sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal, para atender as necessidades da SNPH.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2024NE0000004</t>
+          <t>2024NE0000003</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5115.98</v>
+        <v>9268.620000000001</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6229,19 +6229,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
+          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2024NE0000003</t>
+          <t>2024NE0000004</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>9268.620000000001</v>
+        <v>5115.98</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6259,19 +6259,19 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>REFERENTE SERVIÇOS DE ACESSO À INTERNET POR FIBRA ÓPTICA E FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR PARA SNPH. PARECER Nº 023/2023-PROJU/SNPH. TC: 0002/2020 AD:</t>
+          <t>Serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH. Parecer nº 040/2023-PRUJU/SNPH. TC: 0004/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2023NE0000013</t>
+          <t>2023NE0000007</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>17579.04</v>
+        <v>10231.96</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6289,19 +6289,19 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
+          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2023NE0000007</t>
+          <t>2023NE0000013</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>10231.96</v>
+        <v>17579.04</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6319,19 +6319,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Terceira prorrogação de prazo do Contrato nº 0004/2019 do serviço de execução do Sistema PRODAMRH- Cadastro e Folha de Pagamento de Pessoal da SNPH.</t>
+          <t>REFERENTE A SEGUNDA RENOVAÇÃO DA CONTRATAÇÃO DE INTERNET COM LINK DEDICADO DE 10 (DEZ) MBPS PARA A SEDE DA SNPH.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2020NE00004</t>
+          <t>2020NE00002</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>4/2019</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>17991.2</v>
+        <v>3989.84</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6349,19 +6349,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP)</t>
+          <t>4ª PRORROGAÇÃO DO CONTRATO Nº 006/2015 DA PRESTAÇÃO DE SERVIÇO DE INFORMATICA (WEB SITE - PORTAL DE TRANSPARÊNCIA) PARA ATENDER AS NECESSIDADES DA SNPH.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2020NE00002</t>
+          <t>2020NE00004</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>4/2019</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3989.84</v>
+        <v>17991.2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6379,19 +6379,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>4ª PRORROGAÇÃO DO CONTRATO Nº 006/2015 DA PRESTAÇÃO DE SERVIÇO DE INFORMATICA (WEB SITE - PORTAL DE TRANSPARÊNCIA) PARA ATENDER AS NECESSIDADES DA SNPH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA, SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO (CFPP)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>5242.41</v>
+        <v>1560.75</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6409,19 +6409,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1560.75</v>
+        <v>5242.41</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6439,19 +6439,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2018NE00028</t>
+          <t>2018NE00029</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>3676.43</v>
+        <v>12232.29</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6469,19 +6469,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA, REAJUSTE DE 3,36% RE</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2018NE00029</t>
+          <t>2018NE00028</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>12232.29</v>
+        <v>3676.43</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6499,19 +6499,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA, REAJUSTE DE 3,36% RE</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2017NE00003</t>
+          <t>2017NE00002</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2019.44</v>
+        <v>6762.64</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6529,19 +6529,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM GERENCIAMENTO DE WEBSITE PARA SNPH</t>
+          <t>REFERENTE A EMPRESA ESPECIALIZADA NA EXECUÇÃO DA FOLHA DE PAGAMENTO NO SISTEMA CFPP.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2017NE00002</t>
+          <t>2017NE00003</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6762.64</v>
+        <v>2019.44</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6559,14 +6559,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>REFERENTE A EMPRESA ESPECIALIZADA NA EXECUÇÃO DA FOLHA DE PAGAMENTO NO SISTEMA CFPP.</t>
+          <t>REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM GERENCIAMENTO DE WEBSITE PARA SNPH</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2016NE00410</t>
+          <t>2016NE00409</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>504.86</v>
+        <v>1690.66</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SERVIÇO DE WEBSITE DA PRODAM, PERÍODO DE DEZEMBRO/2016.</t>
+          <t>SERVIÇO DE FOLHA DE PAGAMENTO NO SISTEMA CFPP, PERÍODO DE DEZEMBRO/2016.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2016NE00409</t>
+          <t>2016NE00410</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1690.66</v>
+        <v>504.86</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6611,19 +6611,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SERVIÇO DE FOLHA DE PAGAMENTO NO SISTEMA CFPP, PERÍODO DE DEZEMBRO/2016.</t>
+          <t>SERVIÇO DE WEBSITE DA PRODAM, PERÍODO DE DEZEMBRO/2016.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2017NE00312</t>
+          <t>2017NE00318</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>520.25</v>
+        <v>1747.47</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6641,21 +6641,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2017NE00307</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>6/2015</t>
-        </is>
-      </c>
+          <t>2017NE00310</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -6671,17 +6667,21 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
+          <t>ANULAÇÃO DEVIDO EQUIVOCO NA MODALIDADE.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2017NE00310</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>2017NE00307</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>6/2015</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -6697,19 +6697,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DEVIDO EQUIVOCO NA MODALIDADE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2017NE00318</t>
+          <t>2017NE00312</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1747.47</v>
+        <v>520.25</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2017NE00240</t>
+          <t>2017NE00239</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1040.5</v>
+        <v>3494.94</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2017NE00239</t>
+          <t>2017NE00240</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>3494.94</v>
+        <v>1040.5</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH. REAJUSTE DE 3,36 DO IGPM DO PERÍODO DO CONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARENCIA. REAJUS</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2015NE00375</t>
+          <t>2015NE00377</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>9492.190000000001</v>
+        <v>9037.73</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>anulação total devido a mudança de data do inicio do contrato de 01/07 passado para 01/08/2015.</t>
+          <t>erro na descrição</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2015NE00377</t>
+          <t>2015NE00375</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>9037.73</v>
+        <v>9492.190000000001</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>erro na descrição</t>
+          <t>anulação total devido a mudança de data do inicio do contrato de 01/07 passado para 01/08/2015.</t>
         </is>
       </c>
     </row>
@@ -6966,12 +6966,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2019NE00093</t>
+          <t>2019NE00094</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1560.75</v>
+        <v>5242.41</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6989,19 +6989,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2019NE00094</t>
+          <t>2019NE00093</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>5242.41</v>
+        <v>1560.75</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7019,14 +7019,14 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE PROCESSAMENTO DO SISTEMA DE CFPP - CADASTRO DE FOLHA DE PAGAMENTO, PARA A SNPH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE HOSPEDAGEM DE WEBSITE PARA ARMAZENAMENTO DE DADOS NA INFRAESTRUTURA TECNOLÓGICA DA PRODAM EM ATENDIMENTO A LEI DE TRANSPARÊNCIA.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2015NE00156</t>
+          <t>2015NE00182</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em implantação e processamento do sistema CFPP - cadastro e folha de pessoal para a SNPH.</t>
+          <t>ANULAÇÃO TOTAL POR MODALIDADE NA NOTA DE EMPENHO INCORRETA.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2015NE00183</t>
+          <t>2015NE00188</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em implantação e processamento do sistema CFPP - cadastro e folha de pessoal para a SNPH.</t>
+          <t>ANULAÇÃO PARA CORREÇÃO DE MODALIDADE.</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2015NE00188</t>
+          <t>2015NE00183</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7139,14 +7139,14 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA CORREÇÃO DE MODALIDADE.</t>
+          <t>Contratação de empresa especializada em implantação e processamento do sistema CFPP - cadastro e folha de pessoal para a SNPH.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2015NE00182</t>
+          <t>2015NE00156</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL POR MODALIDADE NA NOTA DE EMPENHO INCORRETA.</t>
+          <t>Contratação de empresa especializada em implantação e processamento do sistema CFPP - cadastro e folha de pessoal para a SNPH.</t>
         </is>
       </c>
     </row>
